--- a/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_5605.xlsx
+++ b/tools/_out/brennancad_20261021/stage/04_DESIGN_TABLES/DesignTable_5605.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1459,6 +1459,15 @@
           <t>5605-02-02-02-FG</t>
         </is>
       </c>
+      <c r="F17" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.33</v>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>5605-02-02-02-FG</t>
@@ -1471,12 +1480,12 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5605-02-02-02 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL3@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL1@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5605-02-02-02 (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5605-02-02-02 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5605-02-02-02 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | TAPDRILL1@BORE = Air-Way per-size tap drill -02 0.33 (A1) | TAPDRILL2@BORE = Air-Way per-size tap drill -02 0.33 (A1) | TAPDRILL3@BORE = Air-Way per-size tap drill -02 0.33 (A1)</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -1496,6 +1505,15 @@
           <t>5605-12-12-12-FG</t>
         </is>
       </c>
+      <c r="F18" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0.91</v>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>5605-12-12-12-FG</t>
@@ -1508,12 +1526,12 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5605-12-12-12 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL3@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL1@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5605-12-12-12 (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5605-12-12-12 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5605-12-12-12 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | TAPDRILL1@BORE = Air-Way per-size tap drill -12 0.91 (A1) | TAPDRILL2@BORE = Air-Way per-size tap drill -12 0.91 (A1) | TAPDRILL3@BORE = Air-Way per-size tap drill -12 0.91 (A1)</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -1533,6 +1551,15 @@
           <t>5605-16-16-16-FG</t>
         </is>
       </c>
+      <c r="F19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="H19" t="n">
+        <v>1.14</v>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>5605-16-16-16-FG</t>
@@ -1545,12 +1572,12 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5605-16-16-16 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL3@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL1@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5605-16-16-16 (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5605-16-16-16 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5605-16-16-16 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | TAPDRILL1@BORE = Air-Way per-size tap drill -16 1.14 (A1) | TAPDRILL2@BORE = Air-Way per-size tap drill -16 1.14 (A1) | TAPDRILL3@BORE = Air-Way per-size tap drill -16 1.14 (A1)</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
@@ -1570,6 +1597,15 @@
           <t>5605-20-20-20-FG</t>
         </is>
       </c>
+      <c r="F20" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.48</v>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>5605-20-20-20-FG</t>
@@ -1582,12 +1618,12 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5605-20-20-20 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL3@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL1@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5605-20-20-20 (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5605-20-20-20 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5605-20-20-20 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | TAPDRILL1@BORE = Air-Way per-size tap drill -20 1.48 (A1) | TAPDRILL2@BORE = Air-Way per-size tap drill -20 1.48 (A1) | TAPDRILL3@BORE = Air-Way per-size tap drill -20 1.48 (A1)</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -1607,6 +1643,15 @@
           <t>5605-32-32-32-FG</t>
         </is>
       </c>
+      <c r="F21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="G21" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="H21" t="n">
+        <v>2.2</v>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>5605-32-32-32-FG</t>
@@ -1619,12 +1664,12 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5605-32-32-32 (differs by -FG suffix) -&gt; dims NOT copied</t>
+          <t>[A1/A9 TAPDRILL 2026-10-21: TAPDRILL3@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL2@BORE] [A1/A9 TAPDRILL 2026-10-21: TAPDRILL1@BORE] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has the same size only as 5605-32-32-32 (differs by -FG suffix) -&gt; dims NOT copied</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5605-32-32-32 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series (e.g. 1501 N1, 2701 Y), so 5605-32-32-32 dims are NOT assumed for this SKU; confirm with OMi/Brennan before modelling | TAPDRILL1@BORE = Air-Way per-size tap drill -32 2.2 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20) | TAPDRILL2@BORE = Air-Way per-size tap drill -32 2.2 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20) | TAPDRILL3@BORE = Air-Way per-size tap drill -32 2.2 (A1, A9: Brennan 5405-24-24 / -32-32 STEPs 1.734 / 2.218 -&gt; nearest Air-Way 1.72 / 2.20)</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
